--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484634_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484634_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9269</v>
+        <v>4.5045</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1997</v>
+        <v>5.5048</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2728</v>
+        <v>-1.0003</v>
       </c>
       <c r="G2" t="n">
         <v>4.4111</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2738</v>
+        <v>-0.6963</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8627</v>
+        <v>0.4423</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4111</v>
+        <v>-1.1386</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1267</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>I. EGIDO MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4881</v>
+        <v>2.2005</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2688</v>
+        <v>2.2005</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7059</v>
+        <v>2.2005</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6035</v>
+        <v>0.3251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1024</v>
+        <v>1.8753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1641</v>
+        <v>2.2005</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4709</v>
+        <v>0.3251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.635</v>
+        <v>1.8753</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1326</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1391</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7828</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3562</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. EGIDO MUÑOZ</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2005</v>
+        <v>1.2491</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2005</v>
+        <v>2.1289</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.8798</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2005</v>
+        <v>-1.7059</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3251</v>
+        <v>-1.6035</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8753</v>
+        <v>-0.1024</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2005</v>
+        <v>0.1641</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3251</v>
+        <v>-0.4709</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8753</v>
+        <v>0.635</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.1326</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.9001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.6429</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.2572</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>G. GARCÍA BURGOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3589</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6685</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3096</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9626</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4462</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5163</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4219</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2969</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3845</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7431</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6413</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5868</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2074</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6206</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8183</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GARCÍA BURGOS</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>-0.1276</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>0.9936</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.1212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-2.5766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-1.2784</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.2983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>-0.1358</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>0.9379</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.0737</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.4409</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.2163</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.2246</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.4604</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.1294</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.3937</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2549</v>
+        <v>-0.3797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9796</v>
+        <v>0.7069</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7248</v>
+        <v>-1.0866</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5766</v>
+        <v>-1.9626</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2784</v>
+        <v>-1.4462</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2983</v>
+        <v>-0.5163</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1358</v>
+        <v>0.4219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9379</v>
+        <v>0.2969</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0737</v>
+        <v>0.125</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4409</v>
+        <v>-2.3845</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2163</v>
+        <v>-1.7431</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2246</v>
+        <v>-0.6413</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8428</v>
+        <v>-0.1518</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1154</v>
+        <v>0.2459</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7274</v>
+        <v>-0.3976</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3937</v>
+        <v>0.8183</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3937</v>
+        <v>-0.1371</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3377</v>
+        <v>-1.2172</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3872</v>
+        <v>-1.0437</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0494</v>
+        <v>-0.1735</v>
       </c>
       <c r="G8" t="n">
         <v>0.433</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0173</v>
+        <v>0.1378</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1637</v>
+        <v>0.5072</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1464</v>
+        <v>-0.3694</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3219</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9789</v>
+        <v>-1.4679</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2668</v>
+        <v>-1.7309</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2879</v>
+        <v>0.2631</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2188</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1266</v>
+        <v>0.3844</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3854</v>
+        <v>0.1505</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2587</v>
+        <v>0.234</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4248</v>
+        <v>-2.1859</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9375</v>
+        <v>-0.649</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4874</v>
+        <v>-1.5369</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8322000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4252</v>
+        <v>-1.1863</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7157</v>
+        <v>-0.4272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7095</v>
+        <v>-0.7591</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9323</v>
+        <v>-2.4183</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5153</v>
+        <v>-1.0756</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.417</v>
+        <v>-1.3427</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8242</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1589</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.494</v>
+        <v>0.9336</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3351</v>
+        <v>-0.2608</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2031</v>
+        <v>-3.2467</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.829</v>
+        <v>-1.0213</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3741</v>
+        <v>-2.2254</v>
       </c>
       <c r="G12" t="n">
         <v>0.8238</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.744</v>
+        <v>-0.7877</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0196</v>
+        <v>-0.2119</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7244</v>
+        <v>-0.5758</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7528</v>
+        <v>-3.3404</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8531</v>
+        <v>-2.5647</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8996</v>
+        <v>-0.7758</v>
       </c>
       <c r="G13" t="n">
         <v>-4.085</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0909</v>
+        <v>-0.6785</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6606</v>
+        <v>-0.3722</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4302</v>
+        <v>-0.3064</v>
       </c>
       <c r="V13" t="n">
         <v>0.5068</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.0133</v>
+        <v>-6.5215</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.9535</v>
+        <v>-4.4369</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0598</v>
+        <v>-2.0845</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7237</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6871</v>
+        <v>0.1789</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4895</v>
+        <v>1.0061</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8024</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.945</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.0207</v>
+        <v>-6.9327</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.0516</v>
+        <v>-1.9388</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.9691</v>
+        <v>-4.9939</v>
       </c>
       <c r="G15" t="n">
         <v>-3.7653</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1342</v>
+        <v>-0.0462</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.342</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3634</v>
+        <v>-0.3882</v>
       </c>
       <c r="V15" t="n">
         <v>-3.3045</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.1092</v>
+        <v>-19.5587</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.151799999999999</v>
+        <v>-2.6011</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.9576</v>
+        <v>-16.9575</v>
       </c>
       <c r="G16" t="n">
         <v>-12.5008</v>
@@ -1702,13 +1702,13 @@
         <v>19.242</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6373</v>
+        <v>1.1877</v>
       </c>
       <c r="T16" t="n">
-        <v>4.838100000000001</v>
+        <v>5.388599999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.2008</v>
+        <v>-4.2007</v>
       </c>
       <c r="V16" t="n">
         <v>-8.245799999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4125</v>
+        <v>5.6296</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0624</v>
+        <v>4.2547</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3501</v>
+        <v>1.3749</v>
       </c>
       <c r="G17" t="n">
         <v>2.8461</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0566</v>
+        <v>0.1604</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1636</v>
+        <v>0.1883</v>
       </c>
       <c r="V17" t="n">
         <v>1.89</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7989</v>
+        <v>3.7358</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2456</v>
+        <v>3.6596</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5533</v>
+        <v>0.0762</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6796</v>
+        <v>-1.1321</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0418</v>
+        <v>-1.6131</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6378</v>
+        <v>0.481</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3256</v>
+        <v>1.776</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2325</v>
+        <v>0.3652</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09320000000000001</v>
+        <v>1.4109</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.646</v>
+        <v>-2.9082</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1907</v>
+        <v>-1.9783</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5446</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1833</v>
+        <v>3.1154</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>3.1154</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3916</v>
+        <v>0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8416</v>
+        <v>0.6165</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.45</v>
+        <v>-0.4425</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9109</v>
+        <v>1.5785</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9109</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7758</v>
+        <v>3.413</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1466</v>
+        <v>2.8582</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6292</v>
+        <v>0.5548</v>
       </c>
       <c r="G19" t="n">
         <v>1.7605</v>
@@ -1936,13 +1936,13 @@
         <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5259</v>
+        <v>1.1631</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2625</v>
+        <v>0.974</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2634</v>
+        <v>0.1891</v>
       </c>
       <c r="V19" t="n">
         <v>1.5889</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4963</v>
+        <v>3.0835</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3261</v>
+        <v>2.7108</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1702</v>
+        <v>0.3727</v>
       </c>
       <c r="G20" t="n">
         <v>4.4981</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.452</v>
+        <v>-0.8648</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4404</v>
+        <v>-0.0558</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0116</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3183</v>
+        <v>3.0281</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2172</v>
+        <v>2.6687</v>
       </c>
       <c r="F21" t="n">
-        <v>0.101</v>
+        <v>0.3594</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1321</v>
+        <v>1.6796</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6131</v>
+        <v>1.0418</v>
       </c>
       <c r="I21" t="n">
-        <v>0.481</v>
+        <v>0.6378</v>
       </c>
       <c r="J21" t="n">
-        <v>1.776</v>
+        <v>2.3256</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3652</v>
+        <v>2.2325</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4109</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9082</v>
+        <v>-0.646</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9783</v>
+        <v>-1.1907</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1154</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1154</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2435</v>
+        <v>-0.3792</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8258</v>
+        <v>0.2647</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4177</v>
+        <v>-0.6439</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5785</v>
+        <v>1.9109</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>1.9109</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.9171</v>
+        <v>1.7859</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3031</v>
+        <v>1.5512</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6139</v>
+        <v>0.2347</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9227</v>
+        <v>-2.2036</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1755</v>
+        <v>-1.3927</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7472</v>
+        <v>-0.8109</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7309</v>
+        <v>-1.1562</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1054</v>
+        <v>-0.0249</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6255</v>
+        <v>-1.1313</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1919</v>
+        <v>-1.0474</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0701</v>
+        <v>-1.3677</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1217</v>
+        <v>0.3204</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1731</v>
+        <v>0.4397</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3107</v>
+        <v>0.4563</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4838</v>
+        <v>-0.0166</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6335</v>
+        <v>1.9005</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0104</v>
+        <v>3.1674</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.7859</v>
+        <v>1.5368</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5512</v>
+        <v>0.9185</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2347</v>
+        <v>0.6183</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2036</v>
+        <v>4.9227</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3927</v>
+        <v>1.1755</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8109</v>
+        <v>3.7472</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1562</v>
+        <v>3.7309</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0249</v>
+        <v>1.1054</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1313</v>
+        <v>2.6255</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0474</v>
+        <v>1.1919</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3677</v>
+        <v>0.0701</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3204</v>
+        <v>1.1217</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6493</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4397</v>
+        <v>-0.5534</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4563</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0166</v>
+        <v>-0.4795</v>
       </c>
       <c r="V23" t="n">
-        <v>1.9005</v>
+        <v>-0.6335</v>
       </c>
       <c r="W23" t="n">
-        <v>3.1674</v>
+        <v>0.0104</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6769</v>
+        <v>0.982</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4574</v>
+        <v>0.6882</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2195</v>
+        <v>0.2938</v>
       </c>
       <c r="G24" t="n">
         <v>0.466</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6061</v>
+        <v>0.9112</v>
       </c>
       <c r="T24" t="n">
-        <v>1.8484</v>
+        <v>1.0792</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2423</v>
+        <v>-0.168</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5357</v>
+        <v>0.3251</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.477</v>
+        <v>0.3251</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0126</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4917</v>
+        <v>0.3251</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2394</v>
+        <v>0.3251</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7311</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2735</v>
+        <v>0.3251</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3937</v>
+        <v>0.3251</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6672</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7818000000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8457</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.455</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6765</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7786</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3251</v>
+        <v>0.1481</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3251</v>
+        <v>-0.7654</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.9135</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3251</v>
+        <v>0.4917</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3251</v>
+        <v>-2.2394</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2.7311</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3251</v>
+        <v>1.2735</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3251</v>
+        <v>-1.3937</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.6672</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>-0.8457</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.0675</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.6795</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1415</v>
+        <v>0.0451</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6462</v>
+        <v>0.3577</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7877</v>
+        <v>-0.3126</v>
       </c>
       <c r="G27" t="n">
         <v>-0.1186</v>
@@ -2560,13 +2560,13 @@
         <v>1.6493</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1066</v>
+        <v>-0.9201</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7315</v>
+        <v>0.4431</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8382</v>
+        <v>-1.3631</v>
       </c>
       <c r="V27" t="n">
         <v>1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.7917</v>
+        <v>-2.9627</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.8465</v>
+        <v>-2.2696</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.9452</v>
+        <v>-0.6931</v>
       </c>
       <c r="G28" t="n">
         <v>-1.0349</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.0238</v>
+        <v>-1.1948</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4404</v>
+        <v>0.1365</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.5833</v>
+        <v>-1.3313</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>20.1093</v>
+        <v>20.7503</v>
       </c>
       <c r="E29" t="n">
-        <v>16.9574</v>
+        <v>16.9577</v>
       </c>
       <c r="F29" t="n">
-        <v>3.1516</v>
+        <v>3.792599999999999</v>
       </c>
       <c r="G29" t="n">
         <v>12.5006</v>
@@ -2716,22 +2716,22 @@
         <v>19.2419</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6373</v>
+        <v>0.003599999999999826</v>
       </c>
       <c r="T29" t="n">
         <v>4.200699999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>-4.837899999999999</v>
+        <v>-4.197</v>
       </c>
       <c r="V29" t="n">
-        <v>8.245800000000001</v>
+        <v>8.245799999999999</v>
       </c>
       <c r="W29" t="n">
         <v>11.7559</v>
       </c>
       <c r="X29" t="n">
-        <v>-3.510299999999999</v>
+        <v>-3.5103</v>
       </c>
     </row>
   </sheetData>
